--- a/Python_Scripts/Radioligand_Binding/data_files/Binding_Printout_Template.xlsx
+++ b/Python_Scripts/Radioligand_Binding/data_files/Binding_Printout_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tlalbert\Documents\PDSP_rewrite\Python_Scripts\Radioligand_Binding\data_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01D336DB-97B5-4955-A9C2-7A9584034EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3265410-92EC-4FD5-8A7E-61E5A2F9302A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -333,14 +333,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -366,21 +363,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -411,9 +396,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -423,14 +405,38 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -440,17 +446,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -775,71 +772,72 @@
     <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.140625" customWidth="1"/>
     <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" customWidth="1"/>
     <col min="5" max="5" width="8.28515625" customWidth="1"/>
     <col min="6" max="6" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.140625" customWidth="1"/>
     <col min="8" max="8" width="10.140625" customWidth="1"/>
     <col min="9" max="9" width="9.28515625" customWidth="1"/>
     <col min="10" max="10" width="8.85546875" customWidth="1"/>
-    <col min="11" max="13" width="8.140625" customWidth="1"/>
+    <col min="11" max="11" width="9" customWidth="1"/>
+    <col min="12" max="13" width="8.140625" customWidth="1"/>
     <col min="14" max="14" width="9.140625" customWidth="1"/>
     <col min="15" max="15" width="3.85546875" customWidth="1"/>
     <col min="16" max="16" width="2.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="40"/>
+      <c r="Q1" s="40"/>
     </row>
     <row r="2" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="30" t="s">
+      <c r="B2" s="23"/>
+      <c r="C2" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="34" t="s">
+      <c r="E2" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="35"/>
-      <c r="G2" s="32" t="s">
+      <c r="F2" s="37"/>
+      <c r="G2" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="40"/>
+      <c r="Q2" s="40"/>
     </row>
     <row r="3" spans="1:17" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
+      <c r="A3" s="2"/>
       <c r="B3" s="1" t="s">
         <v>19</v>
       </c>
@@ -861,630 +859,674 @@
       <c r="H3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="I3" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="28" t="s">
+      <c r="K3" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="L3" s="22" t="s">
+      <c r="L3" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="17" t="s">
+      <c r="M3" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="N3" s="12" t="s">
+      <c r="N3" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O3" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P3" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="Q3" s="13" t="s">
+      <c r="Q3" s="29" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="26"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="21"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="37"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="23"/>
-      <c r="L5" s="23"/>
-      <c r="M5" s="19"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="26"/>
+      <c r="A5" s="39"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="21"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="37"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="19"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="26"/>
+      <c r="A6" s="39"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="21"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="37"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="23"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="26"/>
+      <c r="A7" s="39"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="18"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="21"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="37"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="20"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="26"/>
+      <c r="A8" s="39"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="21"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="37"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="23"/>
-      <c r="L9" s="23"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="26"/>
+      <c r="A9" s="39"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="21"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="37"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="20"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="23"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="26"/>
+      <c r="A10" s="39"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="21"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="37"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="20"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="23"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="26"/>
+      <c r="A11" s="39"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="21"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="35"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="24"/>
-      <c r="M12" s="19"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="26"/>
+      <c r="A12" s="37"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="21"/>
     </row>
     <row r="13" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="33" t="s">
+      <c r="A13" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="33" t="s">
+      <c r="C13" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="33" t="s">
+      <c r="D13" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="33" t="s">
+      <c r="E13" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="33" t="s">
+      <c r="F13" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="33" t="s">
+      <c r="G13" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="H13" s="33" t="s">
+      <c r="H13" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="I13" s="33" t="s">
+      <c r="I13" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="J13" s="33"/>
-      <c r="K13" s="38" t="s">
+      <c r="J13" s="30"/>
+      <c r="K13" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="L13" s="39"/>
-      <c r="M13" s="33" t="s">
+      <c r="L13" s="32"/>
+      <c r="M13" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="N13" s="25"/>
-      <c r="O13" s="27"/>
-      <c r="P13" s="6"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="21"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="33"/>
-      <c r="B14" s="33"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="33"/>
-      <c r="J14" s="33"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="41"/>
-      <c r="M14" s="33"/>
-      <c r="N14" s="25"/>
-      <c r="O14" s="27"/>
-      <c r="P14" s="6"/>
+      <c r="A14" s="30"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="33"/>
+      <c r="L14" s="34"/>
+      <c r="M14" s="30"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="21"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="11"/>
-      <c r="B15" s="10"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="10"/>
-      <c r="O15" s="27"/>
-      <c r="P15" s="6"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="35"/>
+      <c r="L15" s="35"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="21"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="11"/>
-      <c r="B16" s="10"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="31"/>
-      <c r="K16" s="31"/>
-      <c r="L16" s="31"/>
-      <c r="M16" s="10"/>
-      <c r="O16" s="27"/>
-      <c r="P16" s="6"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="11"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="31"/>
-      <c r="J17" s="31"/>
-      <c r="K17" s="31"/>
-      <c r="L17" s="31"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="25"/>
-      <c r="O17" s="27"/>
-      <c r="P17" s="6"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="11"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="31"/>
-      <c r="J18" s="31"/>
-      <c r="K18" s="31"/>
-      <c r="L18" s="31"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="25"/>
-      <c r="O18" s="27"/>
-      <c r="P18" s="6"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="11"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="31"/>
-      <c r="L19" s="31"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="25"/>
-      <c r="O19" s="27"/>
-      <c r="P19" s="6"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="11"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="31"/>
-      <c r="J20" s="31"/>
-      <c r="K20" s="31"/>
-      <c r="L20" s="31"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="25"/>
-      <c r="O20" s="27"/>
-      <c r="P20" s="6"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="11"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="31"/>
-      <c r="J21" s="31"/>
-      <c r="K21" s="31"/>
-      <c r="L21" s="31"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="25"/>
-      <c r="O21" s="27"/>
-      <c r="P21" s="6"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="11"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="31"/>
-      <c r="J22" s="31"/>
-      <c r="K22" s="31"/>
-      <c r="L22" s="31"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="25"/>
-      <c r="O22" s="27"/>
-      <c r="P22" s="6"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="11"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="31"/>
-      <c r="J23" s="31"/>
-      <c r="K23" s="31"/>
-      <c r="L23" s="31"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="25"/>
-      <c r="O23" s="27"/>
-      <c r="P23" s="6"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="11"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="31"/>
-      <c r="J24" s="31"/>
-      <c r="K24" s="31"/>
-      <c r="L24" s="31"/>
-      <c r="M24" s="10"/>
-      <c r="N24" s="25"/>
-      <c r="O24" s="27"/>
-      <c r="P24" s="6"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" s="11"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="31"/>
-      <c r="J25" s="31"/>
-      <c r="K25" s="31"/>
-      <c r="L25" s="31"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="25"/>
-      <c r="O25" s="27"/>
-      <c r="P25" s="6"/>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" s="11"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="31"/>
-      <c r="J26" s="31"/>
-      <c r="K26" s="31"/>
-      <c r="L26" s="31"/>
-      <c r="M26" s="10"/>
-      <c r="N26" s="25"/>
-      <c r="O26" s="27"/>
-      <c r="P26" s="6"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" s="11"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="31"/>
-      <c r="J27" s="31"/>
-      <c r="K27" s="31"/>
-      <c r="L27" s="31"/>
-      <c r="M27" s="10"/>
-      <c r="N27" s="25"/>
-      <c r="O27" s="27"/>
-      <c r="P27" s="6"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" s="11"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="10"/>
-      <c r="N28" s="25"/>
-      <c r="O28" s="27"/>
-      <c r="P28" s="6"/>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" s="11"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="31"/>
-      <c r="J29" s="31"/>
-      <c r="K29" s="31"/>
-      <c r="L29" s="31"/>
-      <c r="M29" s="10"/>
-      <c r="N29" s="25"/>
-      <c r="O29" s="27"/>
-      <c r="P29" s="6"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" s="11"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="31"/>
-      <c r="J30" s="31"/>
-      <c r="K30" s="31"/>
-      <c r="L30" s="31"/>
-      <c r="M30" s="10"/>
-      <c r="N30" s="25"/>
-      <c r="O30" s="27"/>
-      <c r="P30" s="6"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="I31" s="31"/>
-      <c r="J31" s="31"/>
-      <c r="K31" s="31"/>
-      <c r="L31" s="31"/>
-      <c r="M31" s="10"/>
-      <c r="N31" s="25"/>
-      <c r="O31" s="7"/>
-      <c r="P31" s="6"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="I32" s="31"/>
-      <c r="J32" s="31"/>
-      <c r="K32" s="31"/>
-      <c r="L32" s="31"/>
-      <c r="M32" s="10"/>
-      <c r="P32" s="6"/>
-    </row>
-    <row r="33" spans="9:16" x14ac:dyDescent="0.25">
-      <c r="I33" s="31"/>
-      <c r="J33" s="31"/>
-      <c r="K33" s="31"/>
-      <c r="L33" s="31"/>
-      <c r="M33" s="10"/>
-      <c r="P33" s="6"/>
-    </row>
-    <row r="34" spans="9:16" x14ac:dyDescent="0.25">
-      <c r="I34" s="31"/>
-      <c r="J34" s="31"/>
-      <c r="K34" s="31"/>
-      <c r="L34" s="31"/>
-      <c r="M34" s="10"/>
-      <c r="P34" s="6"/>
-    </row>
-    <row r="35" spans="9:16" x14ac:dyDescent="0.25">
-      <c r="I35" s="31"/>
-      <c r="J35" s="31"/>
-      <c r="K35" s="31"/>
-      <c r="L35" s="31"/>
-      <c r="M35" s="10"/>
-      <c r="P35" s="6"/>
-    </row>
-    <row r="36" spans="9:16" x14ac:dyDescent="0.25">
-      <c r="I36" s="11"/>
-      <c r="J36" s="11"/>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="35"/>
+      <c r="L16" s="35"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="21"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="35"/>
+      <c r="L17" s="35"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="21"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="35"/>
+      <c r="K18" s="35"/>
+      <c r="L18" s="35"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="21"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="35"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="20"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="21"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="35"/>
+      <c r="K20" s="35"/>
+      <c r="L20" s="35"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="21"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="35"/>
+      <c r="J21" s="35"/>
+      <c r="K21" s="35"/>
+      <c r="L21" s="35"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="9"/>
+      <c r="O21" s="20"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="21"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="35"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="21"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="35"/>
+      <c r="K23" s="35"/>
+      <c r="L23" s="35"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="9"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="21"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="35"/>
+      <c r="J24" s="35"/>
+      <c r="K24" s="35"/>
+      <c r="L24" s="35"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="9"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="21"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="35"/>
+      <c r="J25" s="35"/>
+      <c r="K25" s="35"/>
+      <c r="L25" s="35"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="21"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="35"/>
+      <c r="J26" s="35"/>
+      <c r="K26" s="35"/>
+      <c r="L26" s="35"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="21"/>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="35"/>
+      <c r="J27" s="35"/>
+      <c r="K27" s="35"/>
+      <c r="L27" s="35"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="9"/>
+      <c r="O27" s="20"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="21"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="35"/>
+      <c r="J28" s="35"/>
+      <c r="K28" s="35"/>
+      <c r="L28" s="35"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="9"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="21"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="35"/>
+      <c r="J29" s="35"/>
+      <c r="K29" s="35"/>
+      <c r="L29" s="35"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="9"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="21"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="35"/>
+      <c r="J30" s="35"/>
+      <c r="K30" s="35"/>
+      <c r="L30" s="35"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="9"/>
+      <c r="O30" s="20"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="21"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="35"/>
+      <c r="J31" s="35"/>
+      <c r="K31" s="35"/>
+      <c r="L31" s="35"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="9"/>
+      <c r="O31" s="20"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="21"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="35"/>
+      <c r="J32" s="35"/>
+      <c r="K32" s="35"/>
+      <c r="L32" s="35"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="9"/>
+      <c r="O32" s="20"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="21"/>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="35"/>
+      <c r="J33" s="35"/>
+      <c r="K33" s="35"/>
+      <c r="L33" s="35"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="9"/>
+      <c r="O33" s="20"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="21"/>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A34" s="6"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="35"/>
+      <c r="J34" s="35"/>
+      <c r="K34" s="35"/>
+      <c r="L34" s="35"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="9"/>
+      <c r="O34" s="20"/>
+      <c r="P34" s="5"/>
+      <c r="Q34" s="21"/>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A35" s="6"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="35"/>
+      <c r="J35" s="35"/>
+      <c r="K35" s="35"/>
+      <c r="L35" s="35"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="9"/>
+      <c r="O35" s="20"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="21"/>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="10"/>
+      <c r="L36" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="57">
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="K13:L14"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="A4:A12"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="K29:L29"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="G2:Q2"/>
-    <mergeCell ref="I13:J14"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I17:J17"/>
     <mergeCell ref="K35:L35"/>
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="K15:L15"/>
@@ -1501,6 +1543,47 @@
     <mergeCell ref="K26:L26"/>
     <mergeCell ref="K27:L27"/>
     <mergeCell ref="K28:L28"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="G2:Q2"/>
+    <mergeCell ref="I13:J14"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="A4:A12"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="K13:L14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="80" orientation="landscape" r:id="rId1"/>
